--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0003T0006Z000C1N5_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0003T0006Z000C1N5_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.70026934104857</v>
+        <v>6.288793767920394</v>
       </c>
       <c r="D2" t="n">
-        <v>46.32655660910233</v>
+        <v>7.528065448979128</v>
       </c>
       <c r="E2" t="n">
-        <v>12.95148674418812</v>
+        <v>2.104616595930569</v>
       </c>
       <c r="F2" t="n">
-        <v>15.48507626859226</v>
+        <v>2.516324893646243</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>37.73357703197608</v>
+        <v>6.131706267696114</v>
       </c>
       <c r="D3" t="n">
-        <v>38.61551600013332</v>
+        <v>6.275021350021665</v>
       </c>
       <c r="E3" t="n">
-        <v>12.95148674418812</v>
+        <v>2.104616595930569</v>
       </c>
       <c r="F3" t="n">
-        <v>15.48507626859226</v>
+        <v>2.516324893646243</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>31.42292986471354</v>
+        <v>5.106226103015951</v>
       </c>
       <c r="D4" t="n">
-        <v>30.50351361718593</v>
+        <v>4.956820962792714</v>
       </c>
       <c r="E4" t="n">
-        <v>12.95148674418812</v>
+        <v>2.104616595930569</v>
       </c>
       <c r="F4" t="n">
-        <v>15.48507626859226</v>
+        <v>2.516324893646243</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>14.76441687560148</v>
+        <v>2.399217742285241</v>
       </c>
       <c r="D5" t="n">
-        <v>12.49205878604772</v>
+        <v>2.029959552732755</v>
       </c>
       <c r="E5" t="n">
-        <v>12.95148674418812</v>
+        <v>2.104616595930569</v>
       </c>
       <c r="F5" t="n">
-        <v>15.48507626859226</v>
+        <v>2.516324893646243</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>18.10195645736096</v>
+        <v>2.941567924321155</v>
       </c>
       <c r="D6" t="n">
-        <v>5.697351778146624</v>
+        <v>0.9258196639488264</v>
       </c>
       <c r="E6" t="n">
-        <v>12.95148674418812</v>
+        <v>2.104616595930569</v>
       </c>
       <c r="F6" t="n">
-        <v>15.48507626859226</v>
+        <v>2.516324893646243</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>46.10312061955164</v>
+        <v>7.491757100677142</v>
       </c>
       <c r="D7" t="n">
-        <v>42.81586613652841</v>
+        <v>6.957578247185866</v>
       </c>
       <c r="E7" t="n">
-        <v>12.95148674418812</v>
+        <v>2.104616595930569</v>
       </c>
       <c r="F7" t="n">
-        <v>15.48507626859226</v>
+        <v>2.516324893646243</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>13.79269745484107</v>
+        <v>2.241313336411674</v>
       </c>
       <c r="D8" t="n">
-        <v>13.75789803014498</v>
+        <v>2.235658429898559</v>
       </c>
       <c r="E8" t="n">
-        <v>12.95148674418812</v>
+        <v>2.104616595930569</v>
       </c>
       <c r="F8" t="n">
-        <v>15.48507626859226</v>
+        <v>2.516324893646243</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>47.82228080303099</v>
+        <v>7.771120630492536</v>
       </c>
       <c r="D9" t="n">
-        <v>45.93497514167634</v>
+        <v>7.464433460522406</v>
       </c>
       <c r="E9" t="n">
-        <v>12.95148674418812</v>
+        <v>2.104616595930569</v>
       </c>
       <c r="F9" t="n">
-        <v>15.48507626859226</v>
+        <v>2.516324893646243</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
